--- a/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T16:22:02+00:00</t>
+    <t>2026-01-13T10:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T10:28:42+00:00</t>
+    <t>2026-01-13T15:49:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T15:49:24+00:00</t>
+    <t>2026-01-15T10:13:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-15T10:13:01+00:00</t>
+    <t>2026-01-15T14:11:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-15T14:11:38+00:00</t>
+    <t>2026-01-15T18:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-15T18:33:49+00:00</t>
+    <t>2026-01-20T10:22:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:22:59+00:00</t>
+    <t>2026-01-20T11:47:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T11:47:28+00:00</t>
+    <t>2026-01-21T07:03:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T07:03:56+00:00</t>
+    <t>2026-01-21T07:53:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T07:53:06+00:00</t>
+    <t>2026-01-22T15:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T15:26:15+00:00</t>
+    <t>2026-01-23T09:45:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T09:45:25+00:00</t>
+    <t>2026-01-23T11:21:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T11:21:14+00:00</t>
+    <t>2026-01-23T13:36:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T13:36:24+00:00</t>
+    <t>2026-01-23T15:09:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JANVIER-2026/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T15:09:47+00:00</t>
+    <t>2026-01-26T14:09:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
